--- a/artfynd/A 6089-2025 artfynd.xlsx
+++ b/artfynd/A 6089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109737451</v>
+        <v>109737492</v>
       </c>
       <c r="B2" t="n">
-        <v>89419</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384543.1064777761</v>
+        <v>384249</v>
       </c>
       <c r="R2" t="n">
-        <v>7027337.058989202</v>
+        <v>7027415</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109737481</v>
+        <v>109737489</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gevsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384423.0619045089</v>
+        <v>384177</v>
       </c>
       <c r="R3" t="n">
-        <v>7027238.960385405</v>
+        <v>7027359</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,29 +843,35 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,37 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109737494</v>
+        <v>109737451</v>
       </c>
       <c r="B4" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384272.938373237</v>
+        <v>384543</v>
       </c>
       <c r="R4" t="n">
-        <v>7027416.881254698</v>
+        <v>7027337</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +956,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109737453</v>
+        <v>109737456</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384579.5318273049</v>
+        <v>384635</v>
       </c>
       <c r="R5" t="n">
-        <v>7027286.781140748</v>
+        <v>7026538</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1053,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109737480</v>
+        <v>109737472</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1093,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384480.9962122829</v>
+        <v>384347</v>
       </c>
       <c r="R6" t="n">
-        <v>7027161.398654441</v>
+        <v>7026839</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1150,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1179,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109737483</v>
+        <v>109737479</v>
       </c>
       <c r="B7" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>384258.474602455</v>
+        <v>384481</v>
       </c>
       <c r="R7" t="n">
-        <v>7027302.851067416</v>
+        <v>7027160</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1247,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109737479</v>
+        <v>109737494</v>
       </c>
       <c r="B8" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384480.9638726215</v>
+        <v>384273</v>
       </c>
       <c r="R8" t="n">
-        <v>7027160.501318675</v>
+        <v>7027417</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1344,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,50 +1373,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109737470</v>
+        <v>109737452</v>
       </c>
       <c r="B9" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gevsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384437.1149106757</v>
+        <v>384562</v>
       </c>
       <c r="R9" t="n">
-        <v>7026443.200226287</v>
+        <v>7027303</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,29 +1444,35 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1571,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109737471</v>
+        <v>109737459</v>
       </c>
       <c r="B10" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,34 +1500,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gevsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384436.3617337651</v>
+        <v>384710</v>
       </c>
       <c r="R10" t="n">
-        <v>7026447.271531085</v>
+        <v>7026443</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,29 +1560,35 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1683,15 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109737491</v>
+        <v>109737471</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1616,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384249.9461008849</v>
+        <v>384436</v>
       </c>
       <c r="R11" t="n">
-        <v>7027415.465457354</v>
+        <v>7026447</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,19 +1673,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,16 +1705,11 @@
         <v>109737450</v>
       </c>
       <c r="B12" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1835,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384562.9703025738</v>
+        <v>384563</v>
       </c>
       <c r="R12" t="n">
-        <v>7027401.480507287</v>
+        <v>7027401</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,19 +1770,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1799,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109737477</v>
+        <v>109737453</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384528.735629019</v>
+        <v>384579</v>
       </c>
       <c r="R13" t="n">
-        <v>7027112.956131884</v>
+        <v>7027287</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1980,19 +1867,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109737456</v>
+        <v>109737454</v>
       </c>
       <c r="B14" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384634.8951836472</v>
+        <v>384624</v>
       </c>
       <c r="R14" t="n">
-        <v>7026537.629173579</v>
+        <v>7027163</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,19 +1964,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1993,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109737458</v>
+        <v>109737455</v>
       </c>
       <c r="B15" t="n">
-        <v>76499</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384639.3053341418</v>
+        <v>384646</v>
       </c>
       <c r="R15" t="n">
-        <v>7026522.642374022</v>
+        <v>7026989</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2204,19 +2061,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,19 +2090,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109737455</v>
+        <v>109737457</v>
       </c>
       <c r="B16" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2283,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384646.1802553227</v>
+        <v>384642</v>
       </c>
       <c r="R16" t="n">
-        <v>7026988.773858321</v>
+        <v>7026521</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2316,19 +2158,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,19 +2187,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109737473</v>
+        <v>109737461</v>
       </c>
       <c r="B17" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2395,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384312.9534702345</v>
+        <v>384728</v>
       </c>
       <c r="R17" t="n">
-        <v>7026880.374689269</v>
+        <v>7026264</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2428,19 +2255,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2284,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109737478</v>
+        <v>109737468</v>
       </c>
       <c r="B18" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2319,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384528.8487705641</v>
+        <v>384438</v>
       </c>
       <c r="R18" t="n">
-        <v>7027116.09685201</v>
+        <v>7026365</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2540,19 +2352,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,37 +2381,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109737492</v>
+        <v>109737473</v>
       </c>
       <c r="B19" t="n">
-        <v>77599</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384249.0476195667</v>
+        <v>384313</v>
       </c>
       <c r="R19" t="n">
-        <v>7027415.497906398</v>
+        <v>7026881</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2652,19 +2449,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,19 +2478,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109737493</v>
+        <v>109737474</v>
       </c>
       <c r="B20" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2731,10 +2513,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384277.0139346343</v>
+        <v>384344</v>
       </c>
       <c r="R20" t="n">
-        <v>7027417.632530836</v>
+        <v>7026931</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2764,19 +2546,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,19 +2575,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109737495</v>
+        <v>109737475</v>
       </c>
       <c r="B21" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2843,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384324.4191491249</v>
+        <v>384470</v>
       </c>
       <c r="R21" t="n">
-        <v>7027447.366256168</v>
+        <v>7026982</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2876,19 +2643,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,19 +2672,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109737468</v>
+        <v>109737480</v>
       </c>
       <c r="B22" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2955,10 +2707,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384438.3610902779</v>
+        <v>384481</v>
       </c>
       <c r="R22" t="n">
-        <v>7026365.416627059</v>
+        <v>7027162</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2988,19 +2740,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,19 +2769,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109737457</v>
+        <v>109737481</v>
       </c>
       <c r="B23" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3067,10 +2804,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384641.9369401959</v>
+        <v>384423</v>
       </c>
       <c r="R23" t="n">
-        <v>7026520.750334962</v>
+        <v>7027239</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3100,19 +2837,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,53 +2866,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109737459</v>
+        <v>109737485</v>
       </c>
       <c r="B24" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gevsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384710.2257615588</v>
+        <v>384193</v>
       </c>
       <c r="R24" t="n">
-        <v>7026442.804403551</v>
+        <v>7027308</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3215,45 +2934,19 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3270,37 +2963,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109737469</v>
+        <v>109737491</v>
       </c>
       <c r="B25" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3310,10 +2998,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384429.6266133726</v>
+        <v>384250</v>
       </c>
       <c r="R25" t="n">
-        <v>7026410.217977958</v>
+        <v>7027415</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3343,19 +3031,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,51 +3060,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109798030</v>
+        <v>109737493</v>
       </c>
       <c r="B26" t="n">
-        <v>78446</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2080</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gevsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384448.1552471851</v>
+        <v>384277</v>
       </c>
       <c r="R26" t="n">
-        <v>7026437.410098647</v>
+        <v>7027418</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3456,26 +3128,11 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>i vid bemärkelse. Troligtvis pallida.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3484,26 +3141,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3520,19 +3157,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109737461</v>
+        <v>109737495</v>
       </c>
       <c r="B27" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3560,10 +3192,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384728.5525256702</v>
+        <v>384325</v>
       </c>
       <c r="R27" t="n">
-        <v>7026264.198749476</v>
+        <v>7027448</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3593,19 +3225,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3632,37 +3254,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109737472</v>
+        <v>109737496</v>
       </c>
       <c r="B28" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3672,10 +3289,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384347.457987856</v>
+        <v>384361</v>
       </c>
       <c r="R28" t="n">
-        <v>7026839.142488383</v>
+        <v>7027503</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3705,19 +3322,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,15 +3351,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109737460</v>
+        <v>109737487</v>
       </c>
       <c r="B29" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,21 +3362,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3784,10 +3386,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384651.5083137136</v>
+        <v>384189</v>
       </c>
       <c r="R29" t="n">
-        <v>7026324.039302698</v>
+        <v>7027331</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3817,19 +3419,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3856,15 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109737476</v>
+        <v>109737469</v>
       </c>
       <c r="B30" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384525.5583230226</v>
+        <v>384430</v>
       </c>
       <c r="R30" t="n">
-        <v>7027112.172079232</v>
+        <v>7026410</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3929,19 +3516,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,37 +3545,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109737496</v>
+        <v>109737470</v>
       </c>
       <c r="B31" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4008,10 +3580,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384361.0499162169</v>
+        <v>384437</v>
       </c>
       <c r="R31" t="n">
-        <v>7027502.644618983</v>
+        <v>7026443</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4041,19 +3613,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,37 +3642,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109737475</v>
+        <v>109737476</v>
       </c>
       <c r="B32" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4120,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>384470.5006064608</v>
+        <v>384526</v>
       </c>
       <c r="R32" t="n">
-        <v>7026982.520940815</v>
+        <v>7027112</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4153,19 +3710,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,53 +3739,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109737452</v>
+        <v>109737483</v>
       </c>
       <c r="B33" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gevsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>384562.1432099803</v>
+        <v>384258</v>
       </c>
       <c r="R33" t="n">
-        <v>7027303.579678726</v>
+        <v>7027303</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4268,45 +3807,19 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4323,15 +3836,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109737454</v>
+        <v>109737458</v>
       </c>
       <c r="B34" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4339,21 +3847,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4363,10 +3871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>384624.1244574337</v>
+        <v>384639</v>
       </c>
       <c r="R34" t="n">
-        <v>7027163.431550057</v>
+        <v>7026523</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4396,19 +3904,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,15 +3933,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109737474</v>
+        <v>109737486</v>
       </c>
       <c r="B35" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4451,21 +3944,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4475,10 +3968,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>384344.0206997666</v>
+        <v>384191</v>
       </c>
       <c r="R35" t="n">
-        <v>7026930.921784734</v>
+        <v>7027334</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4508,19 +4001,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,32 +4030,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109737490</v>
+        <v>109737478</v>
       </c>
       <c r="B36" t="n">
-        <v>89790</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>229497</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4582,10 +4065,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>384216.0099476406</v>
+        <v>384529</v>
       </c>
       <c r="R36" t="n">
-        <v>7027409.952974258</v>
+        <v>7027116</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4615,21 +4098,11 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4638,21 +4111,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4666,6 +4124,349 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>109737477</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gevsjön S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>384529</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7027113</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>109737490</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gevsjön S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>384216</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7027410</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>109798030</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80341</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6331316</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rostania effusa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>A.Košuth. et al.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gevsjön S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>384449</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7026437</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6089-2025 artfynd.xlsx
+++ b/artfynd/A 6089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737492</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737489</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737456</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737472</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737479</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737494</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737452</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737459</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737471</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737450</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737453</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737454</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,6 +2157,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737455</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737457</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2281,6 +2361,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737461</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2378,6 +2463,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737468</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2475,6 +2565,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737473</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2572,6 +2667,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737474</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737475</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2766,6 +2871,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737480</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2863,6 +2973,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737481</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2960,6 +3075,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737485</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3057,6 +3177,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737491</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3154,6 +3279,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737493</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3251,6 +3381,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737495</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3348,6 +3483,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737496</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3445,6 +3585,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737487</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3542,6 +3687,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737469</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3639,6 +3789,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737470</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3736,6 +3891,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737476</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3833,6 +3993,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737483</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3930,6 +4095,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737458</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4027,6 +4197,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737486</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4124,6 +4299,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737478</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4221,6 +4401,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737477</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4333,6 +4518,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737490</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4467,8 +4657,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109798030</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>